--- a/output/pdf_financials_xlsx/HAR.xlsx
+++ b/output/pdf_financials_xlsx/HAR.xlsx
@@ -4746,13 +4746,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.070337</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.070337</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.070337</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
@@ -11647,7 +11647,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
         <v>0.070337</v>
       </c>

--- a/output/pdf_financials_xlsx/HAR.xlsx
+++ b/output/pdf_financials_xlsx/HAR.xlsx
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.01047</v>
+        <v>0.04163</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.009276</v>
+        <v>0.035078</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.008231</v>
+        <v>0.035318</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0.020433</v>
@@ -863,13 +863,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.01047</v>
+        <v>-0.04163</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.009276</v>
+        <v>-0.035078</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.008231</v>
+        <v>-0.035318</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>-0.264857</v>
@@ -918,34 +918,34 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.004334</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.023714</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.051789</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.061521</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.013864</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.035861</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.206594</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.323776</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.243302</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.06758699999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1666,34 +1666,34 @@
         <v>-0.035318</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.260523</v>
+        <v>-0.264857</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.716972</v>
+        <v>-1.740686</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.395991</v>
+        <v>-1.44778</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.491578</v>
+        <v>-1.553099</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.127834</v>
+        <v>-2.141698</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-4.527133</v>
+        <v>-4.562994</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.936054</v>
+        <v>-4.142648</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.589965</v>
+        <v>-2.913741</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.6074</v>
+        <v>-2.850702</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.696922</v>
+        <v>-2.764509</v>
       </c>
     </row>
     <row r="28">
@@ -1758,34 +1758,34 @@
         <v>-0.035318</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.260523</v>
+        <v>-0.264857</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.716972</v>
+        <v>-1.740686</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.395991</v>
+        <v>-1.44778</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.491578</v>
+        <v>-1.553099</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.127834</v>
+        <v>-2.141698</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-4.527133</v>
+        <v>-4.562994</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.936054</v>
+        <v>-4.142648</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.560057</v>
+        <v>-2.883833</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.567523</v>
+        <v>-2.810825</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.66124</v>
+        <v>-2.728827</v>
       </c>
     </row>
     <row r="30">
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-55486.37087878417</v>
+        <v>-55925.89778159088</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-119928.5191956124</v>
+        <v>-126223.2784887264</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -1984,43 +1984,43 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.002354</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.001527</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001049</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.863652</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.489632</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.287057</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.962041</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>8.683052999999999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>7.264839</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>7.413806</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>6.42792</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>3.916888</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.08913</v>
       </c>
     </row>
     <row r="35">
@@ -2076,43 +2076,43 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.002354</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.001527</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001049</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.863652</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.489632</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.287057</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.962041</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>8.683052999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>7.264839</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>7.413806</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>6.42792</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>3.916888</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.08913</v>
       </c>
     </row>
     <row r="37">
@@ -2637,34 +2637,34 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.934355</v>
+        <v>0.070703</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.544816</v>
+        <v>0.055184</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.334833</v>
+        <v>0.047776</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3.008687</v>
+        <v>0.046646</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>8.685703</v>
+        <v>0.00265</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>7.264839</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>7.735604</v>
+        <v>0.321798</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>7.030398</v>
+        <v>0.602478</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>4.024728</v>
+        <v>0.10784</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.138085</v>
+        <v>0.048955</v>
       </c>
     </row>
     <row r="49">
@@ -6209,13 +6209,13 @@
         <v>0</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.038692</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.036444</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.034598</v>
       </c>
     </row>
     <row r="125">
@@ -6255,13 +6255,13 @@
         <v>0</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.038692</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.036444</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.034598</v>
       </c>
     </row>
     <row r="126">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
@@ -14014,7 +14014,11 @@
           <t>Lease payment</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -15398,7 +15402,11 @@
           <t>Lease payment 12</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -23096,7 +23104,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -27773,7 +27781,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -29122,7 +29130,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E285" s="5" t="n">
@@ -29442,17 +29450,17 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E289" s="5" t="n">
-        <v>-0.04163</v>
+        <v>0.04163</v>
       </c>
       <c r="F289" s="5" t="n">
-        <v>-0.035078</v>
+        <v>0.035078</v>
       </c>
       <c r="G289" s="5" t="n">
-        <v>-0.035318</v>
+        <v>0.035318</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/HAR.xlsx
+++ b/output/pdf_financials_xlsx/HAR.xlsx
@@ -1712,19 +1712,19 @@
         <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.000584</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.000583</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.000584</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.000584</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.000583</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0</v>
@@ -1758,19 +1758,19 @@
         <v>-0.035318</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.264857</v>
+        <v>-0.264273</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.740686</v>
+        <v>-1.740103</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.44778</v>
+        <v>-1.447196</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.553099</v>
+        <v>-1.552515</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.141698</v>
+        <v>-2.141115</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-4.562994</v>
@@ -5084,19 +5084,19 @@
         <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.000584</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.000583</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.000584</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.000584</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.000583</v>
       </c>
       <c r="J100" s="3" t="n">
         <v>0</v>
@@ -18093,7 +18093,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -19778,7 +19782,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HAR.xlsx
+++ b/output/pdf_financials_xlsx/HAR.xlsx
@@ -706,16 +706,16 @@
         <v>0.178077</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.380923</v>
+        <v>0.458548</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.396807</v>
+        <v>0.474307</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.476652</v>
+        <v>0.540152</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.347591</v>
+        <v>0.382529</v>
       </c>
     </row>
     <row r="8">
@@ -5562,7 +5562,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.002998</v>
       </c>
       <c r="L110" s="3" t="n">
         <v>0</v>
@@ -12668,7 +12668,11 @@
           <t>Deferred income taxes recovery 10</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -14920,7 +14924,11 @@
           <t>Deferred income taxes recovery 11</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -15734,7 +15742,11 @@
           <t>Finance costs – accretion expense</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -16218,7 +16230,11 @@
           <t>Private placements 13</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -17275,7 +17291,11 @@
           <t>Private placements 10</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -18577,7 +18597,11 @@
           <t>Private placements 9</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -20193,7 +20217,11 @@
           <t>Private placements 11</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -22279,7 +22307,11 @@
           <t>Director’s fees 13</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -24111,7 +24143,11 @@
           <t>Director’s fees 15</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -24911,7 +24947,11 @@
           <t>Director’s fees 16</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -26369,7 +26409,11 @@
           <t>Director’s fees 13</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
